--- a/src/main/resources/网站数据.xlsx
+++ b/src/main/resources/网站数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\gh-ai-analysis\gh-ai-analysis-backend\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA2A9AF-81B1-4DAB-A78A-5D1C37BEE297}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB2C98D-9C1E-4C11-A135-137639D22C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,6 +50,22 @@
   </si>
   <si>
     <t>profit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你他妈的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>傻逼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狗东西</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -375,10 +391,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -391,8 +407,11 @@
       <c r="D1" t="s">
         <v>6</v>
       </c>
+      <c r="E1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -405,8 +424,11 @@
       <c r="D2">
         <v>2000</v>
       </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -419,8 +441,11 @@
       <c r="D3">
         <v>3000</v>
       </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -432,6 +457,9 @@
       </c>
       <c r="D4">
         <v>4000</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/网站数据.xlsx
+++ b/src/main/resources/网站数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\gh-ai-analysis\gh-ai-analysis-backend\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB2C98D-9C1E-4C11-A135-137639D22C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BBA335D-F277-43BC-A2CF-90E6DE2B318A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,22 +50,6 @@
   </si>
   <si>
     <t>profit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你他妈的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>傻逼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>狗东西</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -391,10 +375,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -407,11 +391,8 @@
       <c r="D1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -424,11 +405,8 @@
       <c r="D2">
         <v>2000</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -441,11 +419,8 @@
       <c r="D3">
         <v>3000</v>
       </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -457,9 +432,6 @@
       </c>
       <c r="D4">
         <v>4000</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
